--- a/public/downloads/SanchezCatalyst2020.xlsx
+++ b/public/downloads/SanchezCatalyst2020.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>HO</t>
@@ -659,10 +682,10 @@
         <v>33</v>
       </c>
       <c r="N3" s="5">
-        <v>246.5338399410248</v>
+        <v>246533.8399410248</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03690073940144062</v>
+        <v>36.90073940144062</v>
       </c>
       <c r="P3" s="5">
         <v>6681</v>
@@ -709,10 +732,10 @@
         <v>33</v>
       </c>
       <c r="N4" s="5">
-        <v>497.4370331764221</v>
+        <v>497437.0331764221</v>
       </c>
       <c r="O4" s="4">
-        <v>0.07422217743605224</v>
+        <v>74.22217743605223</v>
       </c>
       <c r="P4" s="5">
         <v>6702</v>
@@ -759,10 +782,10 @@
         <v>33</v>
       </c>
       <c r="N5" s="5">
-        <v>966.0786819458008</v>
+        <v>966078.6819458008</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1370324371554327</v>
+        <v>137.0324371554327</v>
       </c>
       <c r="P5" s="5">
         <v>7050</v>
@@ -809,10 +832,10 @@
         <v>33</v>
       </c>
       <c r="N6" s="5">
-        <v>572.0696601867676</v>
+        <v>572069.6601867676</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08743231853687415</v>
+        <v>87.43231853687415</v>
       </c>
       <c r="P6" s="5">
         <v>6543</v>
@@ -859,10 +882,10 @@
         <v>33</v>
       </c>
       <c r="N7" s="5">
-        <v>1937.325553655624</v>
+        <v>1937325.553655624</v>
       </c>
       <c r="O7" s="4">
-        <v>0.3594962986928232</v>
+        <v>359.4962986928232</v>
       </c>
       <c r="P7" s="5">
         <v>5389</v>
@@ -909,10 +932,10 @@
         <v>33</v>
       </c>
       <c r="N8" s="5">
-        <v>176.8257033824921</v>
+        <v>176825.7033824921</v>
       </c>
       <c r="O8" s="4">
-        <v>0.02514943868332983</v>
+        <v>25.14943868332983</v>
       </c>
       <c r="P8" s="5">
         <v>7031</v>
@@ -959,10 +982,10 @@
         <v>33</v>
       </c>
       <c r="N9" s="5">
-        <v>237.0878291130066</v>
+        <v>237087.8291130066</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03431082910463192</v>
+        <v>34.31082910463192</v>
       </c>
       <c r="P9" s="5">
         <v>6910</v>
@@ -1009,10 +1032,10 @@
         <v>33</v>
       </c>
       <c r="N10" s="5">
-        <v>599.2590267658234</v>
+        <v>599259.0267658234</v>
       </c>
       <c r="O10" s="4">
-        <v>0.1060447755734956</v>
+        <v>106.0447755734956</v>
       </c>
       <c r="P10" s="5">
         <v>5651</v>
@@ -1059,10 +1082,10 @@
         <v>33</v>
       </c>
       <c r="N11" s="5">
-        <v>311.963623046875</v>
+        <v>311963.623046875</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04479018277772793</v>
+        <v>44.79018277772793</v>
       </c>
       <c r="P11" s="5">
         <v>6965</v>
@@ -1109,10 +1132,10 @@
         <v>33</v>
       </c>
       <c r="N12" s="5">
-        <v>154.7090826034546</v>
+        <v>154709.0826034546</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02645051848238239</v>
+        <v>26.45051848238239</v>
       </c>
       <c r="P12" s="5">
         <v>5849</v>
@@ -1159,10 +1182,10 @@
         <v>33</v>
       </c>
       <c r="N13" s="5">
-        <v>479.5722184181213</v>
+        <v>479572.2184181213</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07634069061097123</v>
+        <v>76.34069061097124</v>
       </c>
       <c r="P13" s="5">
         <v>6282</v>
@@ -1209,10 +1232,10 @@
         <v>33</v>
       </c>
       <c r="N14" s="5">
-        <v>4425.301512718201</v>
+        <v>4425301.512718201</v>
       </c>
       <c r="O14" s="4">
-        <v>0.5457944638280958</v>
+        <v>545.7944638280958</v>
       </c>
       <c r="P14" s="5">
         <v>8108</v>
@@ -1259,10 +1282,10 @@
         <v>33</v>
       </c>
       <c r="N15" s="5">
-        <v>2546.739179134369</v>
+        <v>2546739.179134369</v>
       </c>
       <c r="O15" s="4">
-        <v>0.5003416854880882</v>
+        <v>500.3416854880882</v>
       </c>
       <c r="P15" s="5">
         <v>5090</v>
@@ -1309,10 +1332,10 @@
         <v>33</v>
       </c>
       <c r="N16" s="5">
-        <v>860.8635606765747</v>
+        <v>860863.5606765747</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1133013372830448</v>
+        <v>113.3013372830448</v>
       </c>
       <c r="P16" s="5">
         <v>7598</v>
@@ -1359,10 +1382,10 @@
         <v>33</v>
       </c>
       <c r="N17" s="5">
-        <v>585.6485793590546</v>
+        <v>585648.5793590546</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1080333110789623</v>
+        <v>108.0333110789623</v>
       </c>
       <c r="P17" s="5">
         <v>5421</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,107 +1497,161 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3317241371573617</v>
+        <v>0.3114806462778695</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3067614614728307</v>
+        <v>0.2905314726999995</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3668663086980518</v>
+        <v>0.3253613042933572</v>
       </c>
       <c r="E3" s="4">
-        <v>90.96023024594453</v>
+        <v>83.35949764521195</v>
       </c>
       <c r="F3" s="4">
-        <v>83.99931165031872</v>
+        <v>78.92101187403196</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
       </c>
       <c r="H3" s="5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1275751916400182</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2905425357357549</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2602875352502785</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4981427407565935</v>
+        <v>0.292202929027939</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5234674406464218</v>
+        <v>0.2489810305970554</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4604105347500829</v>
+        <v>0.2947474919011541</v>
       </c>
       <c r="E4" s="4">
-        <v>90.2250130821559</v>
+        <v>85.8398744113029</v>
       </c>
       <c r="F4" s="4">
-        <v>83.86766477370527</v>
+        <v>83.31182240578205</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
       </c>
       <c r="H4" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.04574906079022352</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2901670448171634</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2509092872020695</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4829784854662452</v>
+        <v>0.400708393570654</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1534559471209826</v>
+        <v>0.2054584711361844</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2787697736253857</v>
+        <v>0.295645579201107</v>
       </c>
       <c r="E5" s="4">
-        <v>81.54033041788148</v>
+        <v>75.1166180758013</v>
       </c>
       <c r="F5" s="4">
-        <v>69.66123362096613</v>
+        <v>67.25311601150591</v>
       </c>
       <c r="G5" s="5">
         <v>7</v>
@@ -1569,23 +1660,39 @@
         <v>4</v>
       </c>
       <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
         <v>2</v>
       </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.400708393570654</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2054584711361844</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1703,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1711,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1722,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1764,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,107 +1795,161 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.306351455251213</v>
+        <v>0.3077873541522492</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2872326515409895</v>
+        <v>0.2743774303191293</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3554622346466833</v>
+        <v>0.2947748165628092</v>
       </c>
       <c r="E3" s="4">
-        <v>85.83725798011506</v>
+        <v>85.12820512820504</v>
       </c>
       <c r="F3" s="4">
-        <v>78.88401307864434</v>
+        <v>79.66184821889539</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
       </c>
       <c r="H3" s="5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.08864168778731338</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.287982320414124</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2509714813558903</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3507025464743029</v>
+        <v>0.3392166062788096</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2889807834647513</v>
+        <v>0.3478776366817752</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3673922138092263</v>
+        <v>0.3281009725459792</v>
       </c>
       <c r="E4" s="4">
-        <v>87.22396650968079</v>
+        <v>85.86342229199366</v>
       </c>
       <c r="F4" s="4">
-        <v>81.76389605919825</v>
+        <v>81.61331956633956</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
       </c>
       <c r="H4" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2053678699215311</v>
+      </c>
+      <c r="O4" s="5">
+        <v>11</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.315715165474199</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3201032066399627</v>
+      </c>
+      <c r="R4" s="5">
+        <v>11</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5490450590297087</v>
+        <v>0.4442215738763642</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1750934749050733</v>
+        <v>0.2809742594733582</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3305047870238695</v>
+        <v>0.3875989420603706</v>
       </c>
       <c r="E5" s="4">
-        <v>77.41010689990264</v>
+        <v>74.18367346938737</v>
       </c>
       <c r="F5" s="4">
-        <v>66.46372643017008</v>
+        <v>63.19111537232432</v>
       </c>
       <c r="G5" s="5">
         <v>7</v>
@@ -1796,9 +1972,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4442215738763642</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2809742594733582</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2001,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2009,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2020,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2062,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,25 +2093,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3348019993162115</v>
+        <v>0.3317241371573617</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3278085687768556</v>
+        <v>0.3067614614728307</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3510373508775746</v>
+        <v>0.3668663086980518</v>
       </c>
       <c r="E3" s="4">
-        <v>88.70748299319719</v>
+        <v>90.96023024594453</v>
       </c>
       <c r="F3" s="4">
-        <v>84.39855446566894</v>
+        <v>83.99931165031872</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
@@ -1927,25 +2152,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1503875110251942</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3002447795767899</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2969017681549175</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3472705814768434</v>
+        <v>0.4981427407565935</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3681825477112697</v>
+        <v>0.5234674406464218</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3232748599180844</v>
+        <v>0.4604105347500829</v>
       </c>
       <c r="E4" s="4">
-        <v>89.72004186289898</v>
+        <v>90.2250130821559</v>
       </c>
       <c r="F4" s="4">
-        <v>85.58165548098393</v>
+        <v>83.86766477370527</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
@@ -1968,25 +2211,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.4340124421273561</v>
+      </c>
+      <c r="O4" s="5">
+        <v>11</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2891005370517848</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2890431518769964</v>
+      </c>
+      <c r="R4" s="5">
+        <v>11</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.663761292116744</v>
+        <v>0.4829784854662452</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1809425312317217</v>
+        <v>0.1534559471209826</v>
       </c>
       <c r="D5" s="4">
-        <v>0.236168992575017</v>
+        <v>0.2787697736253857</v>
       </c>
       <c r="E5" s="4">
-        <v>81.03498542274052</v>
+        <v>81.54033041788148</v>
       </c>
       <c r="F5" s="4">
-        <v>70.90923617769364</v>
+        <v>69.66123362096613</v>
       </c>
       <c r="G5" s="5">
         <v>7</v>
@@ -1995,23 +2256,39 @@
         <v>4</v>
       </c>
       <c r="I5" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4829784854662452</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1534559471209826</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2299,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2307,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2318,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2360,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,116 +2391,170 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2540869685003774</v>
+        <v>0.306351455251213</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2302381137131533</v>
+        <v>0.2872326515409895</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2713515914087496</v>
+        <v>0.3554622346466833</v>
       </c>
       <c r="E3" s="4">
-        <v>86.96755625327042</v>
+        <v>85.83725798011506</v>
       </c>
       <c r="F3" s="4">
-        <v>83.96747547754281</v>
+        <v>78.88401307864434</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
       </c>
       <c r="H3" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.05564963937689527</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3212694505356108</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2766933692675764</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4173662979181271</v>
+        <v>0.3507025464743029</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3666745867157395</v>
+        <v>0.2889807834647513</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3988356182621784</v>
+        <v>0.3673922138092263</v>
       </c>
       <c r="E4" s="4">
-        <v>87.74201988487695</v>
+        <v>87.22396650968079</v>
       </c>
       <c r="F4" s="4">
-        <v>84.16107382550233</v>
+        <v>81.76389605919825</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
       </c>
       <c r="H4" s="5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1203103008803876</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3029767369190786</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2590426999633612</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.477834696652589</v>
+        <v>0.5490450590297087</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1226046710938249</v>
+        <v>0.1750934749050733</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2147578941522202</v>
+        <v>0.3305047870238695</v>
       </c>
       <c r="E5" s="4">
-        <v>75.45189504373147</v>
+        <v>77.41010689990264</v>
       </c>
       <c r="F5" s="4">
-        <v>68.45957174816223</v>
+        <v>66.46372643017008</v>
       </c>
       <c r="G5" s="5">
         <v>7</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
         <v>3</v>
@@ -2222,9 +2568,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5490450590297087</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1750934749050733</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2597,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2605,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2616,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2658,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,132 +2689,202 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7158298922373038</v>
+        <v>0.3348019993162115</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5123535916474702</v>
+        <v>0.3278085687768556</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6592253498452015</v>
+        <v>0.3510373508775746</v>
       </c>
       <c r="E3" s="4">
-        <v>80.29304029304062</v>
+        <v>88.70748299319719</v>
       </c>
       <c r="F3" s="4">
-        <v>71.95577353295407</v>
+        <v>84.39855446566894</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
       </c>
       <c r="H3" s="5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.03584346314202817</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3320448098437477</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3310670654261309</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.877021123404354</v>
+        <v>0.3472705814768434</v>
       </c>
       <c r="C4" s="4">
-        <v>1.141386925109251</v>
+        <v>0.3681825477112697</v>
       </c>
       <c r="D4" s="4">
-        <v>1.711368082628477</v>
+        <v>0.3232748599180844</v>
       </c>
       <c r="E4" s="4">
-        <v>79.91365777080097</v>
+        <v>89.72004186289898</v>
       </c>
       <c r="F4" s="4">
-        <v>66.98072620891331</v>
+        <v>85.58165548098393</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
       </c>
       <c r="H4" s="5">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.2319772473490657</v>
+      </c>
+      <c r="O4" s="5">
+        <v>11</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2745415318618811</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2822300345299506</v>
+      </c>
+      <c r="R4" s="5">
+        <v>11</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.8930958721634384</v>
+        <v>0.663761292116744</v>
       </c>
       <c r="C5" s="4">
-        <v>0.7861613066932502</v>
+        <v>0.1809425312317217</v>
       </c>
       <c r="D5" s="4">
-        <v>0.369241964567617</v>
+        <v>0.236168992575017</v>
       </c>
       <c r="E5" s="4">
-        <v>69.83479105928042</v>
+        <v>81.03498542274052</v>
       </c>
       <c r="F5" s="4">
-        <v>53.54745925215772</v>
+        <v>70.90923617769364</v>
       </c>
       <c r="G5" s="5">
         <v>7</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5" s="5">
         <v>3</v>
       </c>
       <c r="J5" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.663761292116744</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1809425312317217</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2895,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2903,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2914,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2956,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,66 +2987,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2674465264874558</v>
+        <v>0.2540869685003774</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2827340478832412</v>
+        <v>0.2302381137131533</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2652932471611016</v>
+        <v>0.2713515914087496</v>
       </c>
       <c r="E3" s="4">
-        <v>90.83725798011506</v>
+        <v>86.96755625327042</v>
       </c>
       <c r="F3" s="4">
-        <v>85.85183273102746</v>
+        <v>83.96747547754281</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
       </c>
       <c r="H3" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.07204181831414189</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2493536661394203</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2168806388124949</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2721047045500319</v>
+        <v>0.4173662979181271</v>
       </c>
       <c r="C4" s="4">
-        <v>0.285962930948533</v>
+        <v>0.3666745867157395</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2346172286427267</v>
+        <v>0.3988356182621784</v>
       </c>
       <c r="E4" s="4">
-        <v>91.58555729984293</v>
+        <v>87.74201988487695</v>
       </c>
       <c r="F4" s="4">
-        <v>87.22595078299763</v>
+        <v>84.16107382550233</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
@@ -2607,50 +3105,84 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2375905963690612</v>
+      </c>
+      <c r="O4" s="5">
+        <v>11</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3192662578955281</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2507381757799407</v>
+      </c>
+      <c r="R4" s="5">
+        <v>11</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6965647734121744</v>
+        <v>0.477834696652589</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4575323515976013</v>
+        <v>0.1226046710938249</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4440860759417719</v>
+        <v>0.2147578941522202</v>
       </c>
       <c r="E5" s="4">
-        <v>83.30903790087463</v>
+        <v>75.45189504373147</v>
       </c>
       <c r="F5" s="4">
-        <v>75.1597954618094</v>
+        <v>68.45957174816223</v>
       </c>
       <c r="G5" s="5">
         <v>7</v>
       </c>
       <c r="H5" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
+        <v>3</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
         <v>2</v>
       </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
+      <c r="P5" s="4">
+        <v>0.477834696652589</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1226046710938249</v>
+      </c>
+      <c r="R5" s="5">
         <v>2</v>
       </c>
-      <c r="M5" s="5">
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3193,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3201,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3212,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3254,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,78 +3285,114 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5858278542114638</v>
+        <v>0.7158298922373038</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4536958247993189</v>
+        <v>0.5123535916474702</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6202158140951528</v>
+        <v>0.6592253498452015</v>
       </c>
       <c r="E3" s="4">
-        <v>81.60387231815801</v>
+        <v>80.29304029304062</v>
       </c>
       <c r="F3" s="4">
-        <v>74.91309585269325</v>
+        <v>71.95577353295407</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
       </c>
       <c r="H3" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.4992162377251099</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.406700928901592</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2630835837560196</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.716044974835718</v>
+        <v>1.877021123404354</v>
       </c>
       <c r="C4" s="4">
-        <v>1.426890038920971</v>
+        <v>1.141386925109251</v>
       </c>
       <c r="D4" s="4">
-        <v>1.608974295605101</v>
+        <v>1.711368082628477</v>
       </c>
       <c r="E4" s="4">
-        <v>79.08163265306153</v>
+        <v>79.91365777080097</v>
       </c>
       <c r="F4" s="4">
-        <v>68.37721562553727</v>
+        <v>66.98072620891331</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
       </c>
       <c r="H4" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -2818,27 +3401,45 @@
         <v>7</v>
       </c>
       <c r="M4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>2</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-1.546976179951498</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6750053751999648</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5644243379394509</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4724348271910088</v>
+        <v>0.8930958721634384</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6429908605351127</v>
+        <v>0.7861613066932502</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2724691009713983</v>
+        <v>0.369241964567617</v>
       </c>
       <c r="E5" s="4">
-        <v>73.93100097181733</v>
+        <v>69.83479105928042</v>
       </c>
       <c r="F5" s="4">
-        <v>59.31287951422161</v>
+        <v>53.54745925215772</v>
       </c>
       <c r="G5" s="5">
         <v>7</v>
@@ -2847,23 +3448,39 @@
         <v>1</v>
       </c>
       <c r="I5" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.8930958721634384</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.7861613066932502</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3491,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3499,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3510,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3552,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,66 +3583,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2581704257066875</v>
+        <v>0.2674465264874558</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2802489362546342</v>
+        <v>0.2827340478832412</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2473928332984064</v>
+        <v>0.2652932471611016</v>
       </c>
       <c r="E3" s="4">
-        <v>90.73260073260069</v>
+        <v>90.83725798011506</v>
       </c>
       <c r="F3" s="4">
-        <v>85.55067974530952</v>
+        <v>85.85183273102746</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
       </c>
       <c r="H3" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1681790185093342</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2562552418183332</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2565952379492473</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.295485414491287</v>
+        <v>0.2721047045500319</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3129900054756305</v>
+        <v>0.285962930948533</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2934854826152875</v>
+        <v>0.2346172286427267</v>
       </c>
       <c r="E4" s="4">
-        <v>90.64364207221352</v>
+        <v>91.58555729984293</v>
       </c>
       <c r="F4" s="4">
-        <v>86.47306831870529</v>
+        <v>87.22595078299763</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
@@ -3033,50 +3701,84 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1395247644723044</v>
+      </c>
+      <c r="O4" s="5">
+        <v>11</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2573558230841825</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.268532434670711</v>
+      </c>
+      <c r="R4" s="5">
+        <v>11</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5325335190186229</v>
+        <v>0.6965647734121744</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2110483706377574</v>
+        <v>0.4575323515976013</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2456462431377062</v>
+        <v>0.4440860759417719</v>
       </c>
       <c r="E5" s="4">
-        <v>81.54518950437323</v>
+        <v>83.30903790087463</v>
       </c>
       <c r="F5" s="4">
-        <v>69.74912112496045</v>
+        <v>75.1597954618094</v>
       </c>
       <c r="G5" s="5">
         <v>7</v>
       </c>
       <c r="H5" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6965647734121744</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4575323515976013</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3789,1466 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.5858278542114638</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.4536958247993189</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.6202158140951528</v>
+      </c>
+      <c r="E3" s="4">
+        <v>81.60387231815801</v>
+      </c>
+      <c r="F3" s="4">
+        <v>74.91309585269325</v>
+      </c>
+      <c r="G3" s="5">
+        <v>13</v>
+      </c>
+      <c r="H3" s="5">
+        <v>6</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>7</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>7</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.4536958247993189</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3889982006214159</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2588898727088203</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.716044974835718</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1.426890038920971</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.608974295605101</v>
+      </c>
+      <c r="E4" s="4">
+        <v>79.08163265306153</v>
+      </c>
+      <c r="F4" s="4">
+        <v>68.37721562553727</v>
+      </c>
+      <c r="G4" s="5">
+        <v>13</v>
+      </c>
+      <c r="H4" s="5">
+        <v>5</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>8</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>7</v>
+      </c>
+      <c r="M4" s="5">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-1.55790941894045</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5977744954056431</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5009023348178596</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.4724348271910088</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.6429908605351127</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.2724691009713983</v>
+      </c>
+      <c r="E5" s="4">
+        <v>73.93100097181733</v>
+      </c>
+      <c r="F5" s="4">
+        <v>59.31287951422161</v>
+      </c>
+      <c r="G5" s="5">
+        <v>7</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>4</v>
+      </c>
+      <c r="J5" s="5">
+        <v>2</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>2</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4724348271910088</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6429908605351127</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.2581704257066875</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2802489362546342</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2473928332984064</v>
+      </c>
+      <c r="E3" s="4">
+        <v>90.73260073260069</v>
+      </c>
+      <c r="F3" s="4">
+        <v>85.55067974530952</v>
+      </c>
+      <c r="G3" s="5">
+        <v>13</v>
+      </c>
+      <c r="H3" s="5">
+        <v>11</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>2</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.01705322607505751</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2647293588124788</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2848998160932862</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.295485414491287</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3129900054756305</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2934854826152875</v>
+      </c>
+      <c r="E4" s="4">
+        <v>90.64364207221352</v>
+      </c>
+      <c r="F4" s="4">
+        <v>86.47306831870529</v>
+      </c>
+      <c r="G4" s="5">
+        <v>13</v>
+      </c>
+      <c r="H4" s="5">
+        <v>11</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.1320831024239924</v>
+      </c>
+      <c r="O4" s="5">
+        <v>11</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2741306945925041</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2877526092316143</v>
+      </c>
+      <c r="R4" s="5">
+        <v>11</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.5325335190186229</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.2110483706377574</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.2456462431377062</v>
+      </c>
+      <c r="E5" s="4">
+        <v>81.54518950437323</v>
+      </c>
+      <c r="F5" s="4">
+        <v>69.74912112496045</v>
+      </c>
+      <c r="G5" s="5">
+        <v>7</v>
+      </c>
+      <c r="H5" s="5">
+        <v>3</v>
+      </c>
+      <c r="I5" s="5">
+        <v>3</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5325335190186229</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2110483706377574</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>75.75757575757575</v>
+      </c>
+      <c r="C3" s="3">
+        <v>15.15151515151515</v>
+      </c>
+      <c r="D3" s="3">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.3297759769557211</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.3006878636505808</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.3201280554192509</v>
+      </c>
+      <c r="K3" s="4">
+        <v>85.35044320758595</v>
+      </c>
+      <c r="L3" s="4">
+        <v>78.28892956409797</v>
+      </c>
+      <c r="M3" s="5">
+        <v>33</v>
+      </c>
+      <c r="N3" s="5">
+        <v>246533.8399410248</v>
+      </c>
+      <c r="O3" s="4">
+        <v>36.90073940144062</v>
+      </c>
+      <c r="P3" s="5">
+        <v>6681</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>69.6969696969697</v>
+      </c>
+      <c r="C4" s="3">
+        <v>6.060606060606061</v>
+      </c>
+      <c r="D4" s="3">
+        <v>24.24242424242424</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>24.24242424242424</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.7027171120657569</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.3411803671637358</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.7894310389718746</v>
+      </c>
+      <c r="K4" s="4">
+        <v>85.37518037518029</v>
+      </c>
+      <c r="L4" s="4">
+        <v>78.51603281133406</v>
+      </c>
+      <c r="M4" s="5">
+        <v>33</v>
+      </c>
+      <c r="N4" s="5">
+        <v>497437.0331764221</v>
+      </c>
+      <c r="O4" s="4">
+        <v>74.22217743605223</v>
+      </c>
+      <c r="P4" s="5">
+        <v>6702</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>72.72727272727273</v>
+      </c>
+      <c r="C5" s="3">
+        <v>6.060606060606061</v>
+      </c>
+      <c r="D5" s="3">
+        <v>21.21212121212121</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>21.21212121212121</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.3481315316214363</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.3368445378073364</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.2905118086578432</v>
+      </c>
+      <c r="K5" s="4">
+        <v>83.93836322407742</v>
+      </c>
+      <c r="L5" s="4">
+        <v>77.78489593925765</v>
+      </c>
+      <c r="M5" s="5">
+        <v>33</v>
+      </c>
+      <c r="N5" s="5">
+        <v>966078.6819458008</v>
+      </c>
+      <c r="O5" s="4">
+        <v>137.0324371554327</v>
+      </c>
+      <c r="P5" s="5">
+        <v>7050</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>78.78787878787878</v>
+      </c>
+      <c r="C6" s="3">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="D6" s="3">
+        <v>12.12121212121212</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>12.12121212121212</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.302411596909721</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.2183181490288615</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.22678872922962</v>
+      </c>
+      <c r="K6" s="4">
+        <v>84.5908060193774</v>
+      </c>
+      <c r="L6" s="4">
+        <v>79.67934377330293</v>
+      </c>
+      <c r="M6" s="5">
+        <v>33</v>
+      </c>
+      <c r="N6" s="5">
+        <v>572069.6601867676</v>
+      </c>
+      <c r="O6" s="4">
+        <v>87.43231853687415</v>
+      </c>
+      <c r="P6" s="5">
+        <v>6543</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>84.84848484848484</v>
+      </c>
+      <c r="C7" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="D7" s="3">
+        <v>12.12121212121212</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>12.12121212121212</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.276781550027119</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.2532320707264572</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.2023351141998065</v>
+      </c>
+      <c r="K7" s="4">
+        <v>87.87260358688921</v>
+      </c>
+      <c r="L7" s="4">
+        <v>84.16412446613744</v>
+      </c>
+      <c r="M7" s="5">
+        <v>33</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1937325.553655624</v>
+      </c>
+      <c r="O7" s="4">
+        <v>359.4962986928232</v>
+      </c>
+      <c r="P7" s="5">
+        <v>5389</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>69.6969696969697</v>
+      </c>
+      <c r="C8" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="D8" s="3">
+        <v>27.27272727272727</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>27.27272727272727</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.3137631303691672</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.2466745466877365</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.2995159249121337</v>
+      </c>
+      <c r="K8" s="4">
+        <v>82.58812615955452</v>
+      </c>
+      <c r="L8" s="4">
+        <v>78.17571690054814</v>
+      </c>
+      <c r="M8" s="5">
+        <v>33</v>
+      </c>
+      <c r="N8" s="5">
+        <v>176825.7033824921</v>
+      </c>
+      <c r="O8" s="4">
+        <v>25.14943868332983</v>
+      </c>
+      <c r="P8" s="5">
+        <v>7031</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>75.75757575757575</v>
+      </c>
+      <c r="C9" s="3">
+        <v>6.060606060606061</v>
+      </c>
+      <c r="D9" s="3">
+        <v>18.18181818181818</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>18.18181818181818</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.3320490404146287</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.2849897738549784</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.2976540947133999</v>
+      </c>
+      <c r="K9" s="4">
+        <v>83.09626881055429</v>
+      </c>
+      <c r="L9" s="4">
+        <v>76.93681784285754</v>
+      </c>
+      <c r="M9" s="5">
+        <v>33</v>
+      </c>
+      <c r="N9" s="5">
+        <v>237087.8291130066</v>
+      </c>
+      <c r="O9" s="4">
+        <v>34.31082910463192</v>
+      </c>
+      <c r="P9" s="5">
+        <v>6910</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>78.78787878787878</v>
+      </c>
+      <c r="C10" s="3">
+        <v>6.060606060606061</v>
+      </c>
+      <c r="D10" s="3">
+        <v>15.15151515151515</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>15.15151515151515</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.3346163186192481</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.2715083811090378</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.3041018719209024</v>
+      </c>
+      <c r="K10" s="4">
+        <v>88.67243867243847</v>
+      </c>
+      <c r="L10" s="4">
+        <v>80.90604026845517</v>
+      </c>
+      <c r="M10" s="5">
+        <v>33</v>
+      </c>
+      <c r="N10" s="5">
+        <v>599259.0267658234</v>
+      </c>
+      <c r="O10" s="4">
+        <v>106.0447755734956</v>
+      </c>
+      <c r="P10" s="5">
+        <v>5651</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>60.60606060606061</v>
+      </c>
+      <c r="C11" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="D11" s="3">
+        <v>36.36363636363637</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>36.36363636363637</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.3623792681854219</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.253510583926304</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.3368752480340942</v>
+      </c>
+      <c r="K11" s="4">
+        <v>84.59595959595963</v>
+      </c>
+      <c r="L11" s="4">
+        <v>77.38390617585108</v>
+      </c>
+      <c r="M11" s="5">
+        <v>33</v>
+      </c>
+      <c r="N11" s="5">
+        <v>311963.623046875</v>
+      </c>
+      <c r="O11" s="4">
+        <v>44.79018277772793</v>
+      </c>
+      <c r="P11" s="5">
+        <v>6965</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>78.78787878787878</v>
+      </c>
+      <c r="C12" s="3">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="D12" s="3">
+        <v>12.12121212121212</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>12.12121212121212</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.3797561056663752</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.287309162478607</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.2857492792916375</v>
+      </c>
+      <c r="K12" s="4">
+        <v>87.47887033601317</v>
+      </c>
+      <c r="L12" s="4">
+        <v>82.00325401667703</v>
+      </c>
+      <c r="M12" s="5">
+        <v>33</v>
+      </c>
+      <c r="N12" s="5">
+        <v>154709.0826034546</v>
+      </c>
+      <c r="O12" s="4">
+        <v>26.45051848238239</v>
+      </c>
+      <c r="P12" s="5">
+        <v>5849</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>69.6969696969697</v>
+      </c>
+      <c r="C13" s="3">
+        <v>6.060606060606061</v>
+      </c>
+      <c r="D13" s="3">
+        <v>24.24242424242424</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>24.24242424242424</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.3253606633037107</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.2248754636474759</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.2830392353956561</v>
+      </c>
+      <c r="K13" s="4">
+        <v>84.82993197278886</v>
+      </c>
+      <c r="L13" s="4">
+        <v>80.75418615686992</v>
+      </c>
+      <c r="M13" s="5">
+        <v>33</v>
+      </c>
+      <c r="N13" s="5">
+        <v>479572.2184181213</v>
+      </c>
+      <c r="O13" s="4">
+        <v>76.34069061097124</v>
+      </c>
+      <c r="P13" s="5">
+        <v>6282</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>42.42424242424242</v>
+      </c>
+      <c r="C14" s="3">
+        <v>12.12121212121212</v>
+      </c>
+      <c r="D14" s="3">
+        <v>45.45454545454545</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>45.45454545454545</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.6155713048019488</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.4080679761741901</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.5105937794895924</v>
+      </c>
+      <c r="K14" s="4">
+        <v>77.9251700680268</v>
+      </c>
+      <c r="L14" s="4">
+        <v>66.09111246695072</v>
+      </c>
+      <c r="M14" s="5">
+        <v>33</v>
+      </c>
+      <c r="N14" s="5">
+        <v>4425301.512718201</v>
+      </c>
+      <c r="O14" s="4">
+        <v>545.7944638280958</v>
+      </c>
+      <c r="P14" s="5">
+        <v>8108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>81.81818181818183</v>
+      </c>
+      <c r="C15" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="D15" s="3">
+        <v>15.15151515151515</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>15.15151515151515</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.3500877956853917</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.2912270015984887</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.2646697196324245</v>
+      </c>
+      <c r="K15" s="4">
+        <v>89.53514739229021</v>
+      </c>
+      <c r="L15" s="4">
+        <v>84.12514405802891</v>
+      </c>
+      <c r="M15" s="5">
+        <v>33</v>
+      </c>
+      <c r="N15" s="5">
+        <v>2546739.179134369</v>
+      </c>
+      <c r="O15" s="4">
+        <v>500.3416854880882</v>
+      </c>
+      <c r="P15" s="5">
+        <v>5090</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>39.39393939393939</v>
+      </c>
+      <c r="C16" s="3">
+        <v>12.12121212121212</v>
+      </c>
+      <c r="D16" s="3">
+        <v>48.48484848484848</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>48.48484848484848</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.4889420860208735</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.4001341619765533</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.4769014617612332</v>
+      </c>
+      <c r="K16" s="4">
+        <v>78.98268398268378</v>
+      </c>
+      <c r="L16" s="4">
+        <v>69.02921835807659</v>
+      </c>
+      <c r="M16" s="5">
+        <v>33</v>
+      </c>
+      <c r="N16" s="5">
+        <v>860863.5606765747</v>
+      </c>
+      <c r="O16" s="4">
+        <v>113.3013372830448</v>
+      </c>
+      <c r="P16" s="5">
+        <v>7598</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>75.75757575757575</v>
+      </c>
+      <c r="C17" s="3">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="D17" s="3">
+        <v>15.15151515151515</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>15.15151515151515</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.3252398584059132</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.2772928716194871</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.2588545270077388</v>
+      </c>
+      <c r="K17" s="4">
+        <v>88.74871160585434</v>
+      </c>
+      <c r="L17" s="4">
+        <v>82.56219917293643</v>
+      </c>
+      <c r="M17" s="5">
+        <v>33</v>
+      </c>
+      <c r="N17" s="5">
+        <v>585648.5793590546</v>
+      </c>
+      <c r="O17" s="4">
+        <v>108.0333110789623</v>
+      </c>
+      <c r="P17" s="5">
+        <v>5421</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3847,9 +6003,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>25</v>
+      </c>
+      <c r="C3" s="5">
+        <v>5</v>
+      </c>
+      <c r="D3" s="5">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>3</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>23</v>
+      </c>
+      <c r="C4" s="5">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5">
+        <v>8</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>8</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>6</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>24</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5">
+        <v>7</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>7</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>2</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>26</v>
+      </c>
+      <c r="C6" s="5">
+        <v>3</v>
+      </c>
+      <c r="D6" s="5">
+        <v>4</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>4</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>4</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>28</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>4</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>2</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>23</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5">
+        <v>9</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>9</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>8</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>25</v>
+      </c>
+      <c r="C9" s="5">
+        <v>2</v>
+      </c>
+      <c r="D9" s="5">
+        <v>6</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>6</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>5</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>26</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5">
+        <v>5</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>5</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>3</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>20</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5">
+        <v>12</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>12</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>6</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>26</v>
+      </c>
+      <c r="C12" s="5">
+        <v>3</v>
+      </c>
+      <c r="D12" s="5">
+        <v>4</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>4</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>4</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>23</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5">
+        <v>8</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>8</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>6</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>14</v>
+      </c>
+      <c r="C14" s="5">
+        <v>4</v>
+      </c>
+      <c r="D14" s="5">
+        <v>15</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>15</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>12</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>27</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5">
+        <v>5</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>5</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>3</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>13</v>
+      </c>
+      <c r="C16" s="5">
+        <v>4</v>
+      </c>
+      <c r="D16" s="5">
+        <v>16</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>16</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>13</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>25</v>
+      </c>
+      <c r="C17" s="5">
+        <v>3</v>
+      </c>
+      <c r="D17" s="5">
+        <v>5</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>5</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>2</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6771,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6813,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,10 +6844,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2941521125743258</v>
@@ -3960,10 +6903,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1359061535448621</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2439234291105715</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2343688569744192</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.5918378911412281</v>
@@ -4001,10 +6962,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.5245449041967589</v>
+      </c>
+      <c r="O4" s="5">
+        <v>12</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3230017086117796</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3421472726041609</v>
+      </c>
+      <c r="R4" s="5">
+        <v>12</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.5017972070211759</v>
@@ -4042,9 +7021,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5017972070211759</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4166859466479877</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7050,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7069,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7111,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,10 +7142,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3187273119845031</v>
@@ -4173,10 +7201,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1596392058092161</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3667281278486367</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3001608816580902</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.3810025108019816</v>
@@ -4214,10 +7260,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.3303414893372395</v>
+      </c>
+      <c r="O4" s="5">
+        <v>11</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3480593977294992</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.313875513072504</v>
+      </c>
+      <c r="R4" s="5">
+        <v>11</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>1.985346695093459</v>
@@ -4255,9 +7319,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.985346695093459</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>1.092748102729388</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7348,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7367,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7409,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,10 +7440,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.4103813547793519</v>
@@ -4386,10 +7499,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.186183331824943</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.340386137642235</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3524343035390899</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.4620622741561271</v>
@@ -4427,10 +7558,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.3912795190464692</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3173066084159485</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3528293473480926</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.4197621206787159</v>
@@ -4468,9 +7617,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4197621206787159</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2263993649883863</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7646,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7665,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7707,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,10 +7738,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2360205487810232</v>
@@ -4599,10 +7797,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.0656806271995265</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2208849096448375</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2210881071156336</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.3811110717712198</v>
@@ -4640,10 +7856,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.3152596449499327</v>
+      </c>
+      <c r="O4" s="5">
+        <v>12</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2657331400090153</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2583205872005152</v>
+      </c>
+      <c r="R4" s="5">
+        <v>12</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.5219354360743864</v>
@@ -4681,9 +7915,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5219354360743864</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.09138593929696981</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7944,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7963,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8005,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,10 +8036,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2877357372002595</v>
@@ -4812,10 +8095,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1154527981471305</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2741657488997026</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2932383573063061</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.3973310258599029</v>
@@ -4853,10 +8154,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2757499025645622</v>
+      </c>
+      <c r="O4" s="5">
+        <v>11</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2502982718782609</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2561252509917158</v>
+      </c>
+      <c r="R4" s="5">
+        <v>11</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.2990971126001146</v>
@@ -4894,9 +8213,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1285900240356455</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.330822697254486</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1745830481770933</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8244,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.3114806462778695</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.2905314726999995</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.3253613042933572</v>
-      </c>
-      <c r="E3" s="4">
-        <v>83.35949764521195</v>
-      </c>
-      <c r="F3" s="4">
-        <v>78.92101187403196</v>
-      </c>
-      <c r="G3" s="5">
-        <v>13</v>
-      </c>
-      <c r="H3" s="5">
-        <v>9</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>4</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>4</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.292202929027939</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2489810305970554</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2947474919011541</v>
-      </c>
-      <c r="E4" s="4">
-        <v>85.8398744113029</v>
-      </c>
-      <c r="F4" s="4">
-        <v>83.31182240578205</v>
-      </c>
-      <c r="G4" s="5">
-        <v>13</v>
-      </c>
-      <c r="H4" s="5">
-        <v>10</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>3</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>3</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.400708393570654</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.2054584711361844</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.295645579201107</v>
-      </c>
-      <c r="E5" s="4">
-        <v>75.1166180758013</v>
-      </c>
-      <c r="F5" s="4">
-        <v>67.25311601150591</v>
-      </c>
-      <c r="G5" s="5">
-        <v>7</v>
-      </c>
-      <c r="H5" s="5">
-        <v>4</v>
-      </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>2</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>2</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.3077873541522492</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.2743774303191293</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2947748165628092</v>
-      </c>
-      <c r="E3" s="4">
-        <v>85.12820512820504</v>
-      </c>
-      <c r="F3" s="4">
-        <v>79.66184821889539</v>
-      </c>
-      <c r="G3" s="5">
-        <v>13</v>
-      </c>
-      <c r="H3" s="5">
-        <v>11</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3392166062788096</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3478776366817752</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3281009725459792</v>
-      </c>
-      <c r="E4" s="4">
-        <v>85.86342229199366</v>
-      </c>
-      <c r="F4" s="4">
-        <v>81.61331956633956</v>
-      </c>
-      <c r="G4" s="5">
-        <v>13</v>
-      </c>
-      <c r="H4" s="5">
-        <v>11</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>2</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>2</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.4442215738763642</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.2809742594733582</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.3875989420603706</v>
-      </c>
-      <c r="E5" s="4">
-        <v>74.18367346938737</v>
-      </c>
-      <c r="F5" s="4">
-        <v>63.19111537232432</v>
-      </c>
-      <c r="G5" s="5">
-        <v>7</v>
-      </c>
-      <c r="H5" s="5">
-        <v>3</v>
-      </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>3</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>3</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/SanchezCatalyst2020.xlsx
+++ b/public/downloads/SanchezCatalyst2020.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1275751916400182</v>
+        <v>-0.2114322305856557</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2905425357357549</v>
+        <v>0.2840919942783982</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2602875352502785</v>
+        <v>0.250970086478541</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.04574906079022352</v>
+        <v>0.01659809726677963</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2901670448171634</v>
+        <v>0.2909261523151098</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2509092872020695</v>
+        <v>0.2489810305970554</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -1855,16 +1855,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.08864168778731338</v>
+        <v>-0.1416501558270511</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.287982320414124</v>
+        <v>0.2839047459495287</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2509714813558903</v>
+        <v>0.2461525297159142</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -1914,16 +1914,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2053678699215311</v>
+        <v>0.1336011159655754</v>
       </c>
       <c r="O4" s="5">
         <v>11</v>
       </c>
       <c r="P4" s="4">
-        <v>0.315715165474199</v>
+        <v>0.3027567782151288</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3201032066399627</v>
+        <v>0.3047887489701525</v>
       </c>
       <c r="R4" s="5">
         <v>11</v>
@@ -2153,16 +2153,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1503875110251942</v>
+        <v>0.06659574101996668</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3002447795767899</v>
+        <v>0.3066903003464227</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2969017681549175</v>
+        <v>0.2892843345180787</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -2212,16 +2212,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4340124421273561</v>
+        <v>0.4931810512949824</v>
       </c>
       <c r="O4" s="5">
         <v>11</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2891005370517848</v>
+        <v>0.284549105577352</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2890431518769964</v>
+        <v>0.2836641874072122</v>
       </c>
       <c r="R4" s="5">
         <v>11</v>
@@ -2451,13 +2451,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.05564963937689527</v>
+        <v>-0.08193065620304196</v>
       </c>
       <c r="O3" s="5">
         <v>8</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3212694505356108</v>
+        <v>0.3313775339302826</v>
       </c>
       <c r="Q3" s="4">
         <v>0.2766933692675764</v>
@@ -2510,16 +2510,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1203103008803876</v>
+        <v>0.1558811137537077</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3029767369190786</v>
+        <v>0.2947680877944663</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2590426999633612</v>
+        <v>0.2550903874218812</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -2749,16 +2749,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.03584346314202817</v>
+        <v>-0.07292747498297558</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3320448098437477</v>
+        <v>0.3404118050841327</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3310670654261309</v>
+        <v>0.3211787983238578</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -2808,16 +2808,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2319772473490657</v>
+        <v>0.2199608967382574</v>
       </c>
       <c r="O4" s="5">
         <v>11</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2745415318618811</v>
+        <v>0.2736171971995112</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2822300345299506</v>
+        <v>0.2811376390198772</v>
       </c>
       <c r="R4" s="5">
         <v>11</v>
@@ -3047,13 +3047,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.07204181831414189</v>
+        <v>-0.06725361756411985</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2493536661394203</v>
+        <v>0.2489853430048033</v>
       </c>
       <c r="Q3" s="4">
         <v>0.2168806388124949</v>
@@ -3106,16 +3106,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2375905963690612</v>
+        <v>0.4245543706872468</v>
       </c>
       <c r="O4" s="5">
         <v>11</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3192662578955281</v>
+        <v>0.301350177067307</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2507381757799407</v>
+        <v>0.2295646257102248</v>
       </c>
       <c r="R4" s="5">
         <v>11</v>
@@ -3345,16 +3345,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4992162377251099</v>
+        <v>-0.4041400880310277</v>
       </c>
       <c r="O3" s="5">
         <v>8</v>
       </c>
       <c r="P3" s="4">
-        <v>0.406700928901592</v>
+        <v>0.4205942932244529</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2630835837560196</v>
+        <v>0.2500067446453876</v>
       </c>
       <c r="R3" s="5">
         <v>8</v>
@@ -3404,16 +3404,16 @@
         <v>2</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.546976179951498</v>
+        <v>-1.741269260273384</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6750053751999648</v>
+        <v>0.6002772673838548</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5644243379394509</v>
+        <v>0.5255657218750736</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -3643,16 +3643,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1681790185093342</v>
+        <v>-0.1225998410420193</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2562552418183332</v>
+        <v>0.2438244933939281</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2565952379492473</v>
+        <v>0.2469268586117514</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -3702,16 +3702,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1395247644723044</v>
+        <v>0.09790937783729703</v>
       </c>
       <c r="O4" s="5">
         <v>11</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2573558230841825</v>
+        <v>0.2541546394968742</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.268532434670711</v>
+        <v>0.2647492177038922</v>
       </c>
       <c r="R4" s="5">
         <v>11</v>
@@ -3941,16 +3941,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4536958247993189</v>
+        <v>-0.3427008411179402</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3889982006214159</v>
+        <v>0.4049379301954146</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2588898727088203</v>
+        <v>0.2379284616117948</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -4000,16 +4000,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.55790941894045</v>
+        <v>-1.792623605854544</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5977744954056431</v>
+        <v>0.549078754963915</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5009023348178596</v>
+        <v>0.4494397768749295</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -4239,16 +4239,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.01705322607505751</v>
+        <v>0.05695617211392445</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2647293588124788</v>
+        <v>0.2409279002170103</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2848998160932862</v>
+        <v>0.2702270737875475</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -4298,16 +4298,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1320831024239924</v>
+        <v>0.1549977347924028</v>
       </c>
       <c r="O4" s="5">
         <v>11</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2741306945925041</v>
+        <v>0.2723680305641648</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2877526092316143</v>
+        <v>0.2856694608344861</v>
       </c>
       <c r="R4" s="5">
         <v>11</v>
@@ -4501,13 +4501,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.3297759769557211</v>
+        <v>0.3286549503233824</v>
       </c>
       <c r="I3" s="4">
-        <v>0.3006878636505808</v>
+        <v>0.299367243434956</v>
       </c>
       <c r="J3" s="4">
-        <v>0.3201280554192509</v>
+        <v>0.3212490820515895</v>
       </c>
       <c r="K3" s="4">
         <v>85.35044320758595</v>
@@ -4551,13 +4551,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.7027171120657569</v>
+        <v>0.676635072045995</v>
       </c>
       <c r="I4" s="4">
-        <v>0.3411803671637358</v>
+        <v>0.3245007541454124</v>
       </c>
       <c r="J4" s="4">
-        <v>0.7894310389718746</v>
+        <v>0.7611592250150093</v>
       </c>
       <c r="K4" s="4">
         <v>85.37518037518029</v>
@@ -4601,13 +4601,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.3481315316214363</v>
+        <v>0.3318362095245451</v>
       </c>
       <c r="I5" s="4">
-        <v>0.3368445378073364</v>
+        <v>0.3285309349398797</v>
       </c>
       <c r="J5" s="4">
-        <v>0.2905118086578432</v>
+        <v>0.2881389466353185</v>
       </c>
       <c r="K5" s="4">
         <v>83.93836322407742</v>
@@ -4651,13 +4651,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.302411596909721</v>
+        <v>0.3032101300302226</v>
       </c>
       <c r="I6" s="4">
-        <v>0.2183181490288615</v>
+        <v>0.2176904731881148</v>
       </c>
       <c r="J6" s="4">
-        <v>0.22678872922962</v>
+        <v>0.228013331987263</v>
       </c>
       <c r="K6" s="4">
         <v>84.5908060193774</v>
@@ -4701,13 +4701,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.276781550027119</v>
+        <v>0.2686435811955403</v>
       </c>
       <c r="I7" s="4">
-        <v>0.2532320707264572</v>
+        <v>0.2385067529910572</v>
       </c>
       <c r="J7" s="4">
-        <v>0.2023351141998065</v>
+        <v>0.2013696343358884</v>
       </c>
       <c r="K7" s="4">
         <v>87.87260358688921</v>
@@ -4751,13 +4751,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.3137631303691672</v>
+        <v>0.311521050324551</v>
       </c>
       <c r="I8" s="4">
-        <v>0.2466745466877365</v>
+        <v>0.2421902160357461</v>
       </c>
       <c r="J8" s="4">
-        <v>0.2995159249121337</v>
+        <v>0.2978581650508552</v>
       </c>
       <c r="K8" s="4">
         <v>82.58812615955452</v>
@@ -4801,13 +4801,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.3320490404146287</v>
+        <v>0.3253379039780332</v>
       </c>
       <c r="I9" s="4">
-        <v>0.2849897738549784</v>
+        <v>0.2761310737586723</v>
       </c>
       <c r="J9" s="4">
-        <v>0.2976540947133999</v>
+        <v>0.2975045083731137</v>
       </c>
       <c r="K9" s="4">
         <v>83.09626881055429</v>
@@ -4851,13 +4851,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.3346163186192481</v>
+        <v>0.3353624750082663</v>
       </c>
       <c r="I10" s="4">
-        <v>0.2715083811090378</v>
+        <v>0.2660099049870049</v>
       </c>
       <c r="J10" s="4">
-        <v>0.3041018719209024</v>
+        <v>0.3138310302541638</v>
       </c>
       <c r="K10" s="4">
         <v>88.67243867243847</v>
@@ -4901,13 +4901,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.3623792681854219</v>
+        <v>0.3631275301705968</v>
       </c>
       <c r="I11" s="4">
-        <v>0.253510583926304</v>
+        <v>0.2517320432826381</v>
       </c>
       <c r="J11" s="4">
-        <v>0.3368752480340942</v>
+        <v>0.3345329495582278</v>
       </c>
       <c r="K11" s="4">
         <v>84.59595959595963</v>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.3797561056663752</v>
+        <v>0.3826880628637751</v>
       </c>
       <c r="I12" s="4">
-        <v>0.287309162478607</v>
+        <v>0.2826634975272296</v>
       </c>
       <c r="J12" s="4">
-        <v>0.2857492792916375</v>
+        <v>0.2952734145572194</v>
       </c>
       <c r="K12" s="4">
         <v>87.47887033601317</v>
@@ -5001,13 +5001,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.3253606633037107</v>
+        <v>0.3181577162880472</v>
       </c>
       <c r="I13" s="4">
-        <v>0.2248754636474759</v>
+        <v>0.214748983179351</v>
       </c>
       <c r="J13" s="4">
-        <v>0.2830392353956561</v>
+        <v>0.2816932850784714</v>
       </c>
       <c r="K13" s="4">
         <v>84.82993197278886</v>
@@ -5051,13 +5051,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.6155713048019488</v>
+        <v>0.5916061028197597</v>
       </c>
       <c r="I14" s="4">
-        <v>0.4080679761741901</v>
+        <v>0.3867174195165514</v>
       </c>
       <c r="J14" s="4">
-        <v>0.5105937794895924</v>
+        <v>0.4961851051539833</v>
       </c>
       <c r="K14" s="4">
         <v>77.9251700680268</v>
@@ -5101,13 +5101,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.3500877956853917</v>
+        <v>0.3439297618625955</v>
       </c>
       <c r="I15" s="4">
-        <v>0.2912270015984887</v>
+        <v>0.2853886334990458</v>
       </c>
       <c r="J15" s="4">
-        <v>0.2646697196324245</v>
+        <v>0.2621621633152421</v>
       </c>
       <c r="K15" s="4">
         <v>89.53514739229021</v>
@@ -5151,13 +5151,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.4889420860208735</v>
+        <v>0.4760382029517681</v>
       </c>
       <c r="I16" s="4">
-        <v>0.4001341619765533</v>
+        <v>0.3667077147273429</v>
       </c>
       <c r="J16" s="4">
-        <v>0.4769014617612332</v>
+        <v>0.4731523949966055</v>
       </c>
       <c r="K16" s="4">
         <v>78.98268398268378</v>
@@ -5201,13 +5201,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.3252398584059132</v>
+        <v>0.3151691434328981</v>
       </c>
       <c r="I17" s="4">
-        <v>0.2772928716194871</v>
+        <v>0.2699202797102256</v>
       </c>
       <c r="J17" s="4">
-        <v>0.2588545270077388</v>
+        <v>0.2616568377804081</v>
       </c>
       <c r="K17" s="4">
         <v>88.74871160585434</v>
@@ -6904,16 +6904,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1359061535448621</v>
+        <v>0.1028906481542435</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2439234291105715</v>
+        <v>0.2413837748497547</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2343688569744192</v>
+        <v>0.2313674473934539</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -6963,13 +6963,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.5245449041967589</v>
+        <v>0.5205665307202025</v>
       </c>
       <c r="O4" s="5">
         <v>12</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3230017086117796</v>
+        <v>0.3226956798828138</v>
       </c>
       <c r="Q4" s="4">
         <v>0.3421472726041609</v>
@@ -7202,16 +7202,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1596392058092161</v>
+        <v>-0.04437738203137087</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3667281278486367</v>
+        <v>0.3084863776695714</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3001608816580902</v>
+        <v>0.2684236474174833</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -7261,16 +7261,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3303414893372395</v>
+        <v>0.2958199665624761</v>
       </c>
       <c r="O4" s="5">
         <v>11</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3480593977294992</v>
+        <v>0.3400928924737846</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.313875513072504</v>
+        <v>0.3107371928202528</v>
       </c>
       <c r="R4" s="5">
         <v>11</v>
@@ -7500,16 +7500,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.186183331824943</v>
+        <v>0.3434294209566815</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.340386137642235</v>
+        <v>0.3040985786118339</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3524343035390899</v>
+        <v>0.3381392045271138</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -7559,16 +7559,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3912795190464692</v>
+        <v>0.3675525369314983</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3173066084159485</v>
+        <v>0.3122291190465489</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3528293473480926</v>
+        <v>0.3486013093793702</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -7798,16 +7798,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.0656806271995265</v>
+        <v>0.08278123437924023</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2208849096448375</v>
+        <v>0.2209449892848607</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2210881071156336</v>
+        <v>0.2194561499296924</v>
       </c>
       <c r="R3" s="5">
         <v>10</v>
@@ -7857,13 +7857,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3152596449499327</v>
+        <v>0.3408302026061847</v>
       </c>
       <c r="O4" s="5">
         <v>12</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2657331400090153</v>
+        <v>0.2677001059825732</v>
       </c>
       <c r="Q4" s="4">
         <v>0.2583205872005152</v>
@@ -8096,16 +8096,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1154527981471305</v>
+        <v>0.05501283713863359</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2741657488997026</v>
+        <v>0.275040467091344</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2932383573063061</v>
+        <v>0.2832830313494283</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -8155,16 +8155,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2757499025645622</v>
+        <v>0.217777404709409</v>
       </c>
       <c r="O4" s="5">
         <v>11</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2502982718782609</v>
+        <v>0.2493935986538356</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2561252509917158</v>
+        <v>0.2445156375710036</v>
       </c>
       <c r="R4" s="5">
         <v>11</v>
@@ -8214,16 +8214,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1285900240356455</v>
+        <v>0.03552103145744923</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.330822697254486</v>
+        <v>0.2925136178236422</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1745830481770933</v>
+        <v>0.1454006209374749</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
